--- a/public/magnolia/kitchen.xlsx
+++ b/public/magnolia/kitchen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D36F192-A371-C047-B21B-A83FF139026B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC648DB6-52F3-974F-BEA7-09B804871130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1340" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1340" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="109">
   <si>
     <t>name_ru</t>
   </si>
@@ -196,9 +196,6 @@
   </si>
   <si>
     <t>შოკოლადის ფონდანტი</t>
-  </si>
-  <si>
-    <t>shakshuka2</t>
   </si>
   <si>
     <t>კრემ სუპი ფრიკადელკებით</t>
@@ -1026,13 +1023,13 @@
     </row>
     <row r="3" spans="1:4" ht="19">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -1209,10 +1206,10 @@
         <v>51</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="28">
@@ -1247,8 +1244,9 @@
       <c r="F5" s="3"/>
       <c r="G5" s="14"/>
       <c r="H5" s="11"/>
-      <c r="I5" s="11" t="s">
-        <v>53</v>
+      <c r="I5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>shakshuka</v>
       </c>
       <c r="J5" s="11" t="str">
         <f t="shared" ref="J5:J15" si="1">LOWER($B5)&amp;"_"&amp;2</f>
@@ -1470,10 +1468,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>38</v>
@@ -1561,13 +1559,13 @@
     </row>
     <row r="14" spans="1:30" ht="19">
       <c r="A14" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="29">
@@ -1607,13 +1605,13 @@
     </row>
     <row r="15" spans="1:30" ht="19">
       <c r="A15" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="C15" s="25" t="s">
         <v>88</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>89</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="29">
@@ -29284,13 +29282,13 @@
     </row>
     <row r="3" spans="1:30" ht="20.25" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="28">
@@ -29310,13 +29308,13 @@
     </row>
     <row r="4" spans="1:30" ht="20.25" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="28">
@@ -29336,13 +29334,13 @@
     </row>
     <row r="5" spans="1:30" ht="20.25" customHeight="1">
       <c r="A5" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="28">
@@ -29362,13 +29360,13 @@
     </row>
     <row r="6" spans="1:30" ht="20.25" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="28">
@@ -29388,7 +29386,7 @@
     </row>
     <row r="7" spans="1:30" ht="19">
       <c r="A7" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>42</v>
@@ -29414,13 +29412,13 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="28">
         <v>22</v>
@@ -29459,13 +29457,13 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="28">
         <v>18</v>
@@ -29504,13 +29502,13 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="28">
         <v>26</v>
@@ -29549,13 +29547,13 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="28">
         <v>21</v>
@@ -29594,13 +29592,13 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="28">
         <v>22</v>
@@ -29639,13 +29637,13 @@
     </row>
     <row r="13" spans="1:30" ht="19">
       <c r="A13" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="32" t="s">
         <v>91</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>92</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="29">
@@ -29685,13 +29683,13 @@
     </row>
     <row r="14" spans="1:30" ht="19">
       <c r="A14" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="32" t="s">
         <v>94</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>95</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="29">
@@ -29731,13 +29729,13 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" s="29">
         <v>19</v>
@@ -29776,13 +29774,13 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" s="29">
         <v>22</v>
@@ -29821,13 +29819,13 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" s="29">
         <v>22</v>

--- a/public/magnolia/kitchen.xlsx
+++ b/public/magnolia/kitchen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC648DB6-52F3-974F-BEA7-09B804871130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4241B1D4-3CD9-C347-BDD1-2959A9FDFF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1340" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1340" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -300,9 +300,6 @@
     <t>Креп Сюзет</t>
   </si>
   <si>
-    <t>crêpe suzette</t>
-  </si>
-  <si>
     <t>კრეპ სუზეტი</t>
   </si>
   <si>
@@ -364,6 +361,9 @@
   </si>
   <si>
     <t xml:space="preserve">ქოქოსის ბრინჯი </t>
+  </si>
+  <si>
+    <t>Pancakes Suzette</t>
   </si>
 </sst>
 </file>
@@ -1206,10 +1206,10 @@
         <v>51</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="28">
@@ -1608,10 +1608,10 @@
         <v>86</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="29">
@@ -1622,11 +1622,11 @@
       <c r="H15" s="17"/>
       <c r="I15" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>crêpe suzette</v>
+        <v>pancakes suzette</v>
       </c>
       <c r="J15" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>crêpe suzette_2</v>
+        <v>pancakes suzette_2</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -29282,10 +29282,10 @@
     </row>
     <row r="3" spans="1:30" ht="20.25" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" s="26" t="s">
         <v>53</v>
@@ -29386,7 +29386,7 @@
     </row>
     <row r="7" spans="1:30" ht="19">
       <c r="A7" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>42</v>
@@ -29637,13 +29637,13 @@
     </row>
     <row r="13" spans="1:30" ht="19">
       <c r="A13" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="32" t="s">
         <v>90</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>91</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="29">
@@ -29683,13 +29683,13 @@
     </row>
     <row r="14" spans="1:30" ht="19">
       <c r="A14" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="32" t="s">
         <v>93</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>94</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="29">
@@ -29729,13 +29729,13 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E15" s="29">
         <v>19</v>
@@ -29774,13 +29774,13 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" s="29">
         <v>22</v>
@@ -29819,13 +29819,13 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" s="29">
         <v>22</v>

--- a/public/magnolia/kitchen.xlsx
+++ b/public/magnolia/kitchen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4241B1D4-3CD9-C347-BDD1-2959A9FDFF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0747932-8CF7-BD49-8555-816A330B286C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1340" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,9 +189,6 @@
     <t>Шоколадный фондан</t>
   </si>
   <si>
-    <t>Chocolate Fondant</t>
-  </si>
-  <si>
     <t xml:space="preserve">Кокосовая рисовая каша </t>
   </si>
   <si>
@@ -364,6 +361,9 @@
   </si>
   <si>
     <t>Pancakes Suzette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Fondant </t>
   </si>
 </sst>
 </file>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="3" spans="1:4" ht="19">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -1203,13 +1203,13 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="28">
@@ -1468,10 +1468,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>38</v>
@@ -1517,10 +1517,10 @@
         <v>49</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" s="28">
         <v>15</v>
@@ -1530,11 +1530,11 @@
       <c r="H13" s="17"/>
       <c r="I13" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>chocolate fondant</v>
+        <v xml:space="preserve">chocolate fondant </v>
       </c>
       <c r="J13" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>chocolate fondant_2</v>
+        <v>chocolate fondant _2</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1559,13 +1559,13 @@
     </row>
     <row r="14" spans="1:30" ht="19">
       <c r="A14" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="23" t="s">
         <v>84</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>85</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="29">
@@ -1605,13 +1605,13 @@
     </row>
     <row r="15" spans="1:30" ht="19">
       <c r="A15" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="29">
@@ -29282,13 +29282,13 @@
     </row>
     <row r="3" spans="1:30" ht="20.25" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="28">
@@ -29308,13 +29308,13 @@
     </row>
     <row r="4" spans="1:30" ht="20.25" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="28">
@@ -29334,13 +29334,13 @@
     </row>
     <row r="5" spans="1:30" ht="20.25" customHeight="1">
       <c r="A5" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="28">
@@ -29360,13 +29360,13 @@
     </row>
     <row r="6" spans="1:30" ht="20.25" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="28">
@@ -29386,7 +29386,7 @@
     </row>
     <row r="7" spans="1:30" ht="19">
       <c r="A7" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>42</v>
@@ -29412,13 +29412,13 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="28">
         <v>22</v>
@@ -29457,13 +29457,13 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" s="28">
         <v>18</v>
@@ -29502,13 +29502,13 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" s="28">
         <v>26</v>
@@ -29547,13 +29547,13 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="28">
         <v>21</v>
@@ -29592,13 +29592,13 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="28">
         <v>22</v>
@@ -29637,13 +29637,13 @@
     </row>
     <row r="13" spans="1:30" ht="19">
       <c r="A13" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="32" t="s">
         <v>89</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>90</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="29">
@@ -29683,13 +29683,13 @@
     </row>
     <row r="14" spans="1:30" ht="19">
       <c r="A14" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="32" t="s">
         <v>92</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>93</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="29">
@@ -29729,13 +29729,13 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" s="29">
         <v>19</v>
@@ -29774,13 +29774,13 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16" s="29">
         <v>22</v>
@@ -29819,13 +29819,13 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17" s="29">
         <v>22</v>

--- a/public/magnolia/kitchen.xlsx
+++ b/public/magnolia/kitchen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0747932-8CF7-BD49-8555-816A330B286C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CD3592-AB2D-E648-8D16-4D5887FE389B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1340" windowWidth="16380" windowHeight="14480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="111">
   <si>
     <t>name_ru</t>
   </si>
@@ -363,7 +363,13 @@
     <t>Pancakes Suzette</t>
   </si>
   <si>
-    <t xml:space="preserve">Chocolate Fondant </t>
+    <t>Chocolate Fondant</t>
+  </si>
+  <si>
+    <t>chocolate fondant1</t>
+  </si>
+  <si>
+    <t>chocolate fondant1_2</t>
   </si>
 </sst>
 </file>
@@ -1528,13 +1534,11 @@
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
       <c r="H13" s="17"/>
-      <c r="I13" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">chocolate fondant </v>
+      <c r="I13" s="23" t="s">
+        <v>109</v>
       </c>
-      <c r="J13" s="11" t="str">
-        <f t="shared" si="1"/>
-        <v>chocolate fondant _2</v>
+      <c r="J13" s="23" t="s">
+        <v>110</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
